--- a/revenue-view/output/Nasam_Revenue_View.xlsx
+++ b/revenue-view/output/Nasam_Revenue_View.xlsx
@@ -497,7 +497,7 @@
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Nasam Revenue View — weekly run · 20 Sep 2026</t>
+          <t>Nasam Revenue View — weekly run · 27 Sep 2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr"/>
@@ -510,7 +510,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>The platform read layer is authorised again, so the commission mapping is now checked against the platform's OWN invoices instead of a screenshot — and it holds. Every rate the platform billed in August matches the rate the ledger shows: Alfaris Group 6% on Trendyol and Noon with a 2,500 fee, Inivita 7% on Amazon, Noon and Trendyol with 1,500, Nokush 7% on Amazon, Noon and Salla with no fee, Wadi Halfa 4.5% on Trendyol with the 2,000 fee dropped. The NASAM-ORG-* invoices the platform raises are the same documents Wafeq holds, so there is no second billing stream and nothing uncounted. Two things need a decision — see PLATFORM MAPPING CHECK at the foot of this sheet. Billed is unchanged at 211,873.82: no invoice has been issued, paid or amended since 9 Sep.</t>
+          <t>A quiet week on billing and a busy one on sales. No invoice has been issued, paid or amended since 9 Sep — three weeks now — so billed stays 211,873.82 and the mapping check is unchanged from last week. August has settled: every marketplace figure in the window is identical to last week's, with two small corrections from late activity — Wadi Halfa closed another 948.15 of August retail, and Sonbol's August-from-integration GMV was trimmed 2,923.50 by late cancellations. September, which is outside this window and lands in the close on 4 Oct, is running hard: Sonbol 643,010, SONDOS Salla 99,980, Invita's new Salla store 105,897, and Wadi Halfa 18,265 of retail. On present trend September will be the largest sales month Nasam has had, and almost none of it is invoiced yet.</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Wafeq API snapshot 20 Sep (164 invoices) · platform commission mapping read 20 Sep from the August NASAM-ORG-* invoices (5 clients) · platform sales and purchase orders pulled 20 Sep · Wafeq accounting exports 8 Sep: purchase bills, journal entries, customer-balances statement · churned-brand snapshots 15 Aug (frozen) · Salla Partners export 30 Aug (21 days old — the four trials live then have all since expired) · rate card 17 Aug. The closed-PO export is retired: purchase orders now carry their values in the platform read layer.</t>
+          <t>Wafeq API snapshot 27 Sep (164 invoices, unchanged since 9 Sep) · platform commission mapping read 20 Sep from the August NASAM-ORG-* invoices (5 clients — September invoices are not raised yet) · platform sales and purchase orders pulled 27 Sep · Wafeq accounting exports 8 Sep: purchase bills, journal entries, customer-balances statement · churned-brand snapshots 15 Aug (frozen) · Salla Partners export 30 Aug (28 days old — the four trials live then have all since expired) · rate card 17 Aug. The closed-PO export is retired: purchase orders now carry their values in the platform read layer.</t>
         </is>
       </c>
     </row>
@@ -746,10 +746,10 @@
         <v>6574.55</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>19753.47</v>
+        <v>20701.62</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>74554.89999999999</v>
+        <v>75503.05</v>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
@@ -783,10 +783,10 @@
         <v>219370.18</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>576649.41</v>
+        <v>573725.91</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>1084740.18</v>
+        <v>1081816.68</v>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
@@ -828,10 +828,10 @@
         <v>258316</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>689170.72</v>
+        <v>687195.37</v>
       </c>
       <c r="M6" s="7" t="n">
-        <v>2119437.89</v>
+        <v>2117462.54</v>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
@@ -2012,10 +2012,10 @@
         <v>2154</v>
       </c>
       <c r="L38" s="8" t="n">
-        <v>11619.02</v>
+        <v>12567.17</v>
       </c>
       <c r="M38" s="8" t="n">
-        <v>14872.52</v>
+        <v>15820.67</v>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
@@ -2041,10 +2041,10 @@
         <v>953.85</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>2318.17</v>
+        <v>3266.32</v>
       </c>
       <c r="M39" s="5" t="n">
-        <v>3272.02</v>
+        <v>4220.17</v>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
@@ -2130,10 +2130,10 @@
       <c r="J42" s="5" t="n"/>
       <c r="K42" s="5" t="n"/>
       <c r="L42" s="5" t="n">
-        <v>533634.2</v>
+        <v>530710.7</v>
       </c>
       <c r="M42" s="5" t="n">
-        <v>533634.2</v>
+        <v>530710.7</v>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
@@ -4191,10 +4191,10 @@
       <c r="J102" s="5" t="n"/>
       <c r="K102" s="5" t="n"/>
       <c r="L102" s="5" t="n">
-        <v>177.59</v>
+        <v>215.51</v>
       </c>
       <c r="M102" s="5" t="n">
-        <v>177.59</v>
+        <v>215.51</v>
       </c>
       <c r="N102" s="3" t="inlineStr">
         <is>
@@ -4379,10 +4379,10 @@
         <v>7680.6</v>
       </c>
       <c r="L108" s="7" t="n">
-        <v>13721.98</v>
+        <v>13759.9</v>
       </c>
       <c r="M108" s="7" t="n">
-        <v>214132.63</v>
+        <v>214170.56</v>
       </c>
       <c r="N108" s="3" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
       </c>
       <c r="N128" s="3" t="inlineStr">
         <is>
-          <t>commission off by agreement — 533,634 of sales in 2026-08 earns nothing and is shown for visibility only</t>
+          <t>commission off by agreement — 530,711 of sales in 2026-08 earns nothing and is shown for visibility only</t>
         </is>
       </c>
     </row>
@@ -8152,10 +8152,10 @@
         <v>953.85</v>
       </c>
       <c r="P57" s="12" t="n">
-        <v>2318.17</v>
+        <v>3266.32</v>
       </c>
       <c r="Q57" s="12" t="n">
-        <v>3272.02</v>
+        <v>4220.17</v>
       </c>
       <c r="R57" s="3" t="inlineStr">
         <is>
@@ -8254,10 +8254,10 @@
       <c r="N59" s="17" t="n"/>
       <c r="O59" s="17" t="n"/>
       <c r="P59" s="17" t="n">
-        <v>54.8</v>
+        <v>92.73</v>
       </c>
       <c r="Q59" s="17" t="n">
-        <v>54.8</v>
+        <v>92.73</v>
       </c>
       <c r="R59" s="3" t="inlineStr">
         <is>
@@ -8736,10 +8736,10 @@
       <c r="N70" s="12" t="n"/>
       <c r="O70" s="12" t="n"/>
       <c r="P70" s="12" t="n">
-        <v>533634.2</v>
+        <v>530710.7</v>
       </c>
       <c r="Q70" s="12" t="n">
-        <v>533634.2</v>
+        <v>530710.7</v>
       </c>
       <c r="R70" s="3" t="inlineStr">
         <is>
@@ -14506,10 +14506,10 @@
       <c r="N185" s="17" t="n"/>
       <c r="O185" s="17" t="n"/>
       <c r="P185" s="17" t="n">
-        <v>177.59</v>
+        <v>215.51</v>
       </c>
       <c r="Q185" s="17" t="n">
-        <v>177.59</v>
+        <v>215.51</v>
       </c>
       <c r="R185" s="3" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         <v>7298.95</v>
       </c>
       <c r="P186" s="18" t="n">
-        <v>12872.19</v>
+        <v>12910.11</v>
       </c>
       <c r="Q186" s="18" t="n">
-        <v>212051.41</v>
+        <v>212089.33</v>
       </c>
       <c r="R186" s="3" t="inlineStr">
         <is>
@@ -16254,10 +16254,10 @@
       <c r="J4" s="5" t="n"/>
       <c r="K4" s="5" t="n"/>
       <c r="L4" s="5" t="n">
-        <v>177.59</v>
+        <v>215.51</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>177.59</v>
+        <v>215.51</v>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
@@ -16330,10 +16330,10 @@
         <v>7680.6</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>13721.98</v>
+        <v>13759.9</v>
       </c>
       <c r="M6" s="7" t="n">
-        <v>214132.63</v>
+        <v>214170.56</v>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
@@ -17035,10 +17035,10 @@
         <v>-26657.85</v>
       </c>
       <c r="L31" s="7" t="n">
-        <v>-8369.209999999999</v>
+        <v>-8331.290000000001</v>
       </c>
       <c r="M31" s="7" t="n">
-        <v>-105619.69</v>
+        <v>-105581.76</v>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
@@ -17080,7 +17080,7 @@
         <v>22.37</v>
       </c>
       <c r="L32" s="19" t="n">
-        <v>62.12</v>
+        <v>62.29</v>
       </c>
       <c r="M32" s="20" t="n">
         <v>67</v>

--- a/revenue-view/output/Nasam_Revenue_View.xlsx
+++ b/revenue-view/output/Nasam_Revenue_View.xlsx
@@ -497,7 +497,7 @@
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Nasam Revenue View — weekly run · 11 Oct 2026</t>
+          <t>Nasam Revenue View — weekly run · 18 Oct 2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr"/>
@@ -510,7 +510,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>September is billed. Four of the five invoices drafted last week were released, putting 10,148.67 into billed and taking it to 222,022.49 — the first movement in a month. Three things worth reading. Dar Sonbol's 8,000 is the one invoice NOT released, so a client with 681,572 of September sales has still never been charged a fee. Wadi Halfa's 2,000 monthly fee was drafted and then dropped on release for the second month running, so zero is what that client actually pays whatever the rate card says. And Inivita's Noon line came down 15.40 on release, recalculated against settled GMV — so the platform does true up marketplace lines when it issues, which answers half of the cancellation question. Collections restarted too: 10,552.78 came in, Ancy &amp; Shaya clearing their whole 7,012.27 balance, though new September invoicing means receivables only fell to 66,525.03. The expense side is still waiting on the October accounting drop.</t>
+          <t>Nasam has signed a client. مستودع الصفا للأدوية المحدودة (Al Safa) was invoiced 5,499 on 13 Oct — a setup fee for onboarding to Amazon, Trendyol and Noon with inventory integration. It is the first new client to be billed since the churn began in February, and the first setup fee since Dar Sonbol in June. The invoice is dated October, so it sits outside this window and is shown as a memo under the revenue streams rather than in any total; it enters billed when October closes. Nothing else moved on billing: the window stays at 222,022.49 and Dar Sonbol's 8,000 is still the one September invoice in draft, now a fortnight old. One small reversal — 0.27 of the Ancy &amp; Shaya balance settled last week has reopened, leaving that account all but clear. September sales continue to settle downward as late cancellations land: Sonbol 677,237 and SONDOS Trendyol 39,243, both trimmed again this week.</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Wafeq API snapshot 11 Oct (169 invoices; 4 September drafts released, 4 older invoices paid) · platform commission mapping read 11 Oct from the September invoices as issued (5 clients) · platform sales and purchase orders pulled 11 Oct · Wafeq accounting exports 8 Sep: purchase bills, journal entries, customer-balances statement · churned-brand snapshots 15 Aug (frozen) · Salla Partners export 30 Aug (42 days old — the four trials live then have all since expired) · rate card 17 Aug. The closed-PO export is retired: purchase orders now carry their values in the platform read layer.</t>
+          <t>Wafeq API snapshot 18 Oct (170 invoices — one new client, INV-000193) · platform commission mapping read 11 Oct from the September invoices as issued (5 clients; no October invoices raised yet) · platform sales and purchase orders pulled 18 Oct · Wafeq accounting exports 8 Sep: purchase bills, journal entries, customer-balances statement · churned-brand snapshots 15 Aug (frozen) · Salla Partners export 30 Aug (49 days old — the four trials live then have all since expired) · rate card 17 Aug. The closed-PO export is retired: purchase orders now carry their values in the platform read layer.</t>
         </is>
       </c>
     </row>
@@ -573,7 +573,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O134"/>
+  <dimension ref="A1:O136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -710,10 +710,10 @@
         <v>92767.84</v>
       </c>
       <c r="M3" s="5" t="n">
-        <v>306989.71</v>
+        <v>306339.35</v>
       </c>
       <c r="N3" s="5" t="n">
-        <v>1267284.93</v>
+        <v>1266634.57</v>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
@@ -823,13 +823,13 @@
         <v>220575.12</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>600263.86</v>
+        <v>600568.0600000001</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>838470.58</v>
+        <v>834135.42</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>1948030.15</v>
+        <v>1943999.19</v>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
@@ -871,13 +871,13 @@
         <v>259520.94</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>713568.3199999999</v>
+        <v>713872.52</v>
       </c>
       <c r="M7" s="7" t="n">
-        <v>1172044.57</v>
+        <v>1167059.05</v>
       </c>
       <c r="N7" s="7" t="n">
-        <v>3317237.41</v>
+        <v>3312556.09</v>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         <v>112057.45</v>
       </c>
       <c r="M9" s="8" t="n">
-        <v>232821.07</v>
+        <v>232170.71</v>
       </c>
       <c r="N9" s="8" t="n">
-        <v>851647.25</v>
+        <v>850996.89</v>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
@@ -1289,10 +1289,10 @@
         <v>60173.92</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>199091.93</v>
+        <v>198441.57</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>646833.5</v>
+        <v>646183.14</v>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
@@ -1487,10 +1487,10 @@
         <v>20575.62</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>39893.79</v>
+        <v>39243.43</v>
       </c>
       <c r="N23" s="5" t="n">
-        <v>79872.42</v>
+        <v>79222.06</v>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
@@ -2270,13 +2270,13 @@
       <c r="J43" s="5" t="n"/>
       <c r="K43" s="5" t="n"/>
       <c r="L43" s="5" t="n">
-        <v>556932.3</v>
+        <v>557236.5</v>
       </c>
       <c r="M43" s="5" t="n">
-        <v>681572.34</v>
+        <v>677237.1800000001</v>
       </c>
       <c r="N43" s="5" t="n">
-        <v>1238504.64</v>
+        <v>1234473.68</v>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
@@ -4386,37 +4386,22 @@
     <row r="103">
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>Retail commission — closed POs, to invoice</t>
-        </is>
-      </c>
-      <c r="C103" s="5" t="n"/>
-      <c r="D103" s="5" t="n"/>
-      <c r="E103" s="5" t="n"/>
-      <c r="F103" s="5" t="n"/>
-      <c r="G103" s="5" t="n"/>
-      <c r="H103" s="5" t="n"/>
-      <c r="I103" s="5" t="n"/>
-      <c r="J103" s="5" t="n"/>
-      <c r="K103" s="5" t="n"/>
-      <c r="L103" s="5" t="n">
-        <v>177.36</v>
-      </c>
-      <c r="M103" s="5" t="n">
-        <v>771.01</v>
+          <t>Memo: issued after the window closed (Oct 2026) — not in any total above</t>
+        </is>
       </c>
       <c r="N103" s="5" t="n">
-        <v>948.38</v>
+        <v>5499</v>
       </c>
       <c r="O103" s="3" t="inlineStr">
         <is>
-          <t>Nasam platform — closed POs — net of retail already billed in Wafeq</t>
+          <t>Wafeq invoice export — enters the totals when that month closes</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>SaaS subscriptions (Salla App Store, gross)</t>
+          <t>Retail commission — closed POs, to invoice</t>
         </is>
       </c>
       <c r="C104" s="5" t="n"/>
@@ -4425,30 +4410,28 @@
       <c r="F104" s="5" t="n"/>
       <c r="G104" s="5" t="n"/>
       <c r="H104" s="5" t="n"/>
-      <c r="I104" s="5" t="n">
-        <v>999.75</v>
-      </c>
+      <c r="I104" s="5" t="n"/>
       <c r="J104" s="5" t="n"/>
-      <c r="K104" s="5" t="n">
-        <v>449</v>
-      </c>
+      <c r="K104" s="5" t="n"/>
       <c r="L104" s="5" t="n">
-        <v>999.75</v>
-      </c>
-      <c r="M104" s="5" t="n"/>
+        <v>177.36</v>
+      </c>
+      <c r="M104" s="5" t="n">
+        <v>771.01</v>
+      </c>
       <c r="N104" s="5" t="n">
-        <v>2448.5</v>
+        <v>948.38</v>
       </c>
       <c r="O104" s="3" t="inlineStr">
         <is>
-          <t>Salla Partners export</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" outlineLevel="1">
+          <t>Nasam platform — closed POs — net of retail already billed in Wafeq</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    محمصة نقوش (Nokush) — annual, paid May 2026</t>
+          <t>SaaS subscriptions (Salla App Store, gross)</t>
         </is>
       </c>
       <c r="C105" s="5" t="n"/>
@@ -4461,11 +4444,15 @@
         <v>999.75</v>
       </c>
       <c r="J105" s="5" t="n"/>
-      <c r="K105" s="5" t="n"/>
-      <c r="L105" s="5" t="n"/>
+      <c r="K105" s="5" t="n">
+        <v>449</v>
+      </c>
+      <c r="L105" s="5" t="n">
+        <v>999.75</v>
+      </c>
       <c r="M105" s="5" t="n"/>
       <c r="N105" s="5" t="n">
-        <v>999.75</v>
+        <v>2448.5</v>
       </c>
       <c r="O105" s="3" t="inlineStr">
         <is>
@@ -4476,7 +4463,7 @@
     <row r="106" outlineLevel="1">
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    SONDOS — monthly, paid Jul 2026</t>
+          <t xml:space="preserve">    محمصة نقوش (Nokush) — annual, paid May 2026</t>
         </is>
       </c>
       <c r="C106" s="5" t="n"/>
@@ -4485,15 +4472,15 @@
       <c r="F106" s="5" t="n"/>
       <c r="G106" s="5" t="n"/>
       <c r="H106" s="5" t="n"/>
-      <c r="I106" s="5" t="n"/>
+      <c r="I106" s="5" t="n">
+        <v>999.75</v>
+      </c>
       <c r="J106" s="5" t="n"/>
-      <c r="K106" s="5" t="n">
-        <v>449</v>
-      </c>
+      <c r="K106" s="5" t="n"/>
       <c r="L106" s="5" t="n"/>
       <c r="M106" s="5" t="n"/>
       <c r="N106" s="5" t="n">
-        <v>449</v>
+        <v>999.75</v>
       </c>
       <c r="O106" s="3" t="inlineStr">
         <is>
@@ -4504,7 +4491,7 @@
     <row r="107" outlineLevel="1">
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    SONDOS — annual, paid Aug 2026</t>
+          <t xml:space="preserve">    SONDOS — monthly, paid Jul 2026</t>
         </is>
       </c>
       <c r="C107" s="5" t="n"/>
@@ -4515,13 +4502,13 @@
       <c r="H107" s="5" t="n"/>
       <c r="I107" s="5" t="n"/>
       <c r="J107" s="5" t="n"/>
-      <c r="K107" s="5" t="n"/>
-      <c r="L107" s="5" t="n">
-        <v>999.75</v>
-      </c>
+      <c r="K107" s="5" t="n">
+        <v>449</v>
+      </c>
+      <c r="L107" s="5" t="n"/>
       <c r="M107" s="5" t="n"/>
       <c r="N107" s="5" t="n">
-        <v>999.75</v>
+        <v>449</v>
       </c>
       <c r="O107" s="3" t="inlineStr">
         <is>
@@ -4529,10 +4516,10 @@
         </is>
       </c>
     </row>
-    <row r="108">
+    <row r="108" outlineLevel="1">
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>less: Salla share (15%)</t>
+          <t xml:space="preserve">    SONDOS — annual, paid Aug 2026</t>
         </is>
       </c>
       <c r="C108" s="5" t="n"/>
@@ -4541,170 +4528,150 @@
       <c r="F108" s="5" t="n"/>
       <c r="G108" s="5" t="n"/>
       <c r="H108" s="5" t="n"/>
-      <c r="I108" s="5" t="n">
-        <v>-149.96</v>
-      </c>
+      <c r="I108" s="5" t="n"/>
       <c r="J108" s="5" t="n"/>
-      <c r="K108" s="5" t="n">
-        <v>-67.34999999999999</v>
-      </c>
+      <c r="K108" s="5" t="n"/>
       <c r="L108" s="5" t="n">
-        <v>-149.96</v>
+        <v>999.75</v>
       </c>
       <c r="M108" s="5" t="n"/>
       <c r="N108" s="5" t="n">
+        <v>999.75</v>
+      </c>
+      <c r="O108" s="3" t="inlineStr">
+        <is>
+          <t>Salla Partners export</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>less: Salla share (15%)</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="n"/>
+      <c r="D109" s="5" t="n"/>
+      <c r="E109" s="5" t="n"/>
+      <c r="F109" s="5" t="n"/>
+      <c r="G109" s="5" t="n"/>
+      <c r="H109" s="5" t="n"/>
+      <c r="I109" s="5" t="n">
+        <v>-149.96</v>
+      </c>
+      <c r="J109" s="5" t="n"/>
+      <c r="K109" s="5" t="n">
+        <v>-67.34999999999999</v>
+      </c>
+      <c r="L109" s="5" t="n">
+        <v>-149.96</v>
+      </c>
+      <c r="M109" s="5" t="n"/>
+      <c r="N109" s="5" t="n">
         <v>-367.27</v>
       </c>
-      <c r="O108" s="3" t="inlineStr">
+      <c r="O109" s="3" t="inlineStr">
         <is>
           <t>15% per Tarik — not pullable from Salla</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="B109" s="6" t="inlineStr">
+    <row r="110">
+      <c r="B110" s="6" t="inlineStr">
         <is>
           <t>TOTAL REVENUE</t>
         </is>
       </c>
-      <c r="C109" s="7" t="n">
+      <c r="C110" s="7" t="n">
         <v>31390.44</v>
       </c>
-      <c r="D109" s="7" t="n">
+      <c r="D110" s="7" t="n">
         <v>21947.73</v>
       </c>
-      <c r="E109" s="7" t="n">
+      <c r="E110" s="7" t="n">
         <v>26212.8</v>
       </c>
-      <c r="F109" s="7" t="n">
+      <c r="F110" s="7" t="n">
         <v>19517.67</v>
       </c>
-      <c r="G109" s="7" t="n">
+      <c r="G110" s="7" t="n">
         <v>27125.53</v>
       </c>
-      <c r="H109" s="7" t="n">
+      <c r="H110" s="7" t="n">
         <v>27486.22</v>
       </c>
-      <c r="I109" s="7" t="n">
+      <c r="I110" s="7" t="n">
         <v>22806.22</v>
       </c>
-      <c r="J109" s="7" t="n">
+      <c r="J110" s="7" t="n">
         <v>16243.45</v>
       </c>
-      <c r="K109" s="7" t="n">
+      <c r="K110" s="7" t="n">
         <v>7680.6</v>
       </c>
-      <c r="L109" s="7" t="n">
+      <c r="L110" s="7" t="n">
         <v>13721.75</v>
       </c>
-      <c r="M109" s="7" t="n">
+      <c r="M110" s="7" t="n">
         <v>10919.68</v>
       </c>
-      <c r="N109" s="7" t="n">
+      <c r="N110" s="7" t="n">
         <v>225052.09</v>
       </c>
-      <c r="O109" s="3" t="inlineStr">
+      <c r="O110" s="3" t="inlineStr">
         <is>
           <t>Billed + to-invoice + SaaS net of Salla share</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="B111" s="1" t="inlineStr">
+    <row r="112">
+      <c r="B112" s="1" t="inlineStr">
         <is>
           <t>BY CLIENT (billed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="B112" s="3" t="inlineStr">
-        <is>
-          <t>Alfaris Group</t>
-        </is>
-      </c>
-      <c r="C112" s="5" t="n">
-        <v>2500</v>
-      </c>
-      <c r="D112" s="5" t="n">
-        <v>2717.44</v>
-      </c>
-      <c r="E112" s="5" t="n">
-        <v>5230.11</v>
-      </c>
-      <c r="F112" s="5" t="n">
-        <v>3123.95</v>
-      </c>
-      <c r="G112" s="5" t="n">
-        <v>2640.55</v>
-      </c>
-      <c r="H112" s="5" t="n">
-        <v>2840.27</v>
-      </c>
-      <c r="I112" s="5" t="n">
-        <v>4081.37</v>
-      </c>
-      <c r="J112" s="5" t="n">
-        <v>3921.48</v>
-      </c>
-      <c r="K112" s="5" t="n">
-        <v>3290.53</v>
-      </c>
-      <c r="L112" s="5" t="n">
-        <v>8741.110000000001</v>
-      </c>
-      <c r="M112" s="5" t="n">
-        <v>6992.82</v>
-      </c>
-      <c r="N112" s="5" t="n">
-        <v>46079.63</v>
-      </c>
-      <c r="O112" s="3" t="inlineStr">
-        <is>
-          <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>Inivita</t>
+          <t>Alfaris Group</t>
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>3269.61</v>
+        <v>2500</v>
       </c>
       <c r="D113" s="5" t="n">
-        <v>3598.8</v>
+        <v>2717.44</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>3591.47</v>
+        <v>5230.11</v>
       </c>
       <c r="F113" s="5" t="n">
-        <v>4252.12</v>
+        <v>3123.95</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>3792.64</v>
+        <v>2640.55</v>
       </c>
       <c r="H113" s="5" t="n">
-        <v>3047.98</v>
+        <v>2840.27</v>
       </c>
       <c r="I113" s="5" t="n">
-        <v>3218.29</v>
+        <v>4081.37</v>
       </c>
       <c r="J113" s="5" t="n">
-        <v>2377.85</v>
+        <v>3921.48</v>
       </c>
       <c r="K113" s="5" t="n">
-        <v>2884.13</v>
+        <v>3290.53</v>
       </c>
       <c r="L113" s="5" t="n">
-        <v>3540.51</v>
+        <v>8741.110000000001</v>
       </c>
       <c r="M113" s="5" t="n">
-        <v>2997.11</v>
+        <v>6992.82</v>
       </c>
       <c r="N113" s="5" t="n">
-        <v>36570.51</v>
+        <v>46079.63</v>
       </c>
       <c r="O113" s="3" t="inlineStr">
         <is>
@@ -4715,44 +4682,44 @@
     <row r="114">
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>Nokush</t>
+          <t>Inivita</t>
         </is>
       </c>
       <c r="C114" s="5" t="n">
-        <v>338.91</v>
+        <v>3269.61</v>
       </c>
       <c r="D114" s="5" t="n">
-        <v>238.59</v>
+        <v>3598.8</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>180.02</v>
+        <v>3591.47</v>
       </c>
       <c r="F114" s="5" t="n">
-        <v>409.44</v>
+        <v>4252.12</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>326.25</v>
+        <v>3792.64</v>
       </c>
       <c r="H114" s="5" t="n">
-        <v>420.69</v>
+        <v>3047.98</v>
       </c>
       <c r="I114" s="5" t="n">
-        <v>655.84</v>
+        <v>3218.29</v>
       </c>
       <c r="J114" s="5" t="n">
-        <v>423.72</v>
+        <v>2377.85</v>
       </c>
       <c r="K114" s="5" t="n">
-        <v>319.26</v>
+        <v>2884.13</v>
       </c>
       <c r="L114" s="5" t="n">
-        <v>237.77</v>
+        <v>3540.51</v>
       </c>
       <c r="M114" s="5" t="n">
-        <v>120.59</v>
+        <v>2997.11</v>
       </c>
       <c r="N114" s="5" t="n">
-        <v>3671.08</v>
+        <v>36570.51</v>
       </c>
       <c r="O114" s="3" t="inlineStr">
         <is>
@@ -4763,36 +4730,44 @@
     <row r="115">
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>Wadi Halfa</t>
-        </is>
-      </c>
-      <c r="C115" s="5" t="n"/>
-      <c r="D115" s="5" t="n"/>
-      <c r="E115" s="5" t="n"/>
-      <c r="F115" s="5" t="n"/>
+          <t>Nokush</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="n">
+        <v>338.91</v>
+      </c>
+      <c r="D115" s="5" t="n">
+        <v>238.59</v>
+      </c>
+      <c r="E115" s="5" t="n">
+        <v>180.02</v>
+      </c>
+      <c r="F115" s="5" t="n">
+        <v>409.44</v>
+      </c>
       <c r="G115" s="5" t="n">
-        <v>3290.32</v>
+        <v>326.25</v>
       </c>
       <c r="H115" s="5" t="n">
-        <v>8.960000000000001</v>
+        <v>420.69</v>
       </c>
       <c r="I115" s="5" t="n">
-        <v>2024.04</v>
+        <v>655.84</v>
       </c>
       <c r="J115" s="5" t="n">
-        <v>2016.48</v>
+        <v>423.72</v>
       </c>
       <c r="K115" s="5" t="n">
-        <v>805.03</v>
+        <v>319.26</v>
       </c>
       <c r="L115" s="5" t="n">
-        <v>175.21</v>
+        <v>237.77</v>
       </c>
       <c r="M115" s="5" t="n">
-        <v>38.15</v>
+        <v>120.59</v>
       </c>
       <c r="N115" s="5" t="n">
-        <v>8358.190000000001</v>
+        <v>3671.08</v>
       </c>
       <c r="O115" s="3" t="inlineStr">
         <is>
@@ -4803,24 +4778,36 @@
     <row r="116">
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>Dar Sonbol</t>
+          <t>Wadi Halfa</t>
         </is>
       </c>
       <c r="C116" s="5" t="n"/>
       <c r="D116" s="5" t="n"/>
       <c r="E116" s="5" t="n"/>
       <c r="F116" s="5" t="n"/>
-      <c r="G116" s="5" t="n"/>
-      <c r="H116" s="5" t="n"/>
-      <c r="I116" s="5" t="n"/>
+      <c r="G116" s="5" t="n">
+        <v>3290.32</v>
+      </c>
+      <c r="H116" s="5" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="I116" s="5" t="n">
+        <v>2024.04</v>
+      </c>
       <c r="J116" s="5" t="n">
-        <v>4000</v>
-      </c>
-      <c r="K116" s="5" t="n"/>
-      <c r="L116" s="5" t="n"/>
-      <c r="M116" s="5" t="n"/>
+        <v>2016.48</v>
+      </c>
+      <c r="K116" s="5" t="n">
+        <v>805.03</v>
+      </c>
+      <c r="L116" s="5" t="n">
+        <v>175.21</v>
+      </c>
+      <c r="M116" s="5" t="n">
+        <v>38.15</v>
+      </c>
       <c r="N116" s="5" t="n">
-        <v>4000</v>
+        <v>8358.190000000001</v>
       </c>
       <c r="O116" s="3" t="inlineStr">
         <is>
@@ -4831,36 +4818,24 @@
     <row r="117">
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>Two United  (churned 2026-05)</t>
-        </is>
-      </c>
-      <c r="C117" s="5" t="n">
-        <v>5000</v>
-      </c>
-      <c r="D117" s="5" t="n">
-        <v>5000</v>
-      </c>
-      <c r="E117" s="5" t="n">
-        <v>3606.59</v>
-      </c>
-      <c r="F117" s="5" t="n">
-        <v>2747.96</v>
-      </c>
-      <c r="G117" s="5" t="n">
-        <v>5631.76</v>
-      </c>
-      <c r="H117" s="5" t="n">
-        <v>5324.76</v>
-      </c>
-      <c r="I117" s="5" t="n">
-        <v>5462.25</v>
-      </c>
-      <c r="J117" s="5" t="n"/>
+          <t>Dar Sonbol</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="n"/>
+      <c r="D117" s="5" t="n"/>
+      <c r="E117" s="5" t="n"/>
+      <c r="F117" s="5" t="n"/>
+      <c r="G117" s="5" t="n"/>
+      <c r="H117" s="5" t="n"/>
+      <c r="I117" s="5" t="n"/>
+      <c r="J117" s="5" t="n">
+        <v>4000</v>
+      </c>
       <c r="K117" s="5" t="n"/>
       <c r="L117" s="5" t="n"/>
       <c r="M117" s="5" t="n"/>
       <c r="N117" s="5" t="n">
-        <v>32773.32</v>
+        <v>4000</v>
       </c>
       <c r="O117" s="3" t="inlineStr">
         <is>
@@ -4871,38 +4846,36 @@
     <row r="118">
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>Rimath  (churned 2026-06)</t>
+          <t>Two United  (churned 2026-05)</t>
         </is>
       </c>
       <c r="C118" s="5" t="n">
-        <v>3743.36</v>
+        <v>5000</v>
       </c>
       <c r="D118" s="5" t="n">
-        <v>2998.75</v>
+        <v>5000</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>3561.57</v>
+        <v>3606.59</v>
       </c>
       <c r="F118" s="5" t="n">
-        <v>4753.24</v>
+        <v>2747.96</v>
       </c>
       <c r="G118" s="5" t="n">
-        <v>3970.51</v>
+        <v>5631.76</v>
       </c>
       <c r="H118" s="5" t="n">
-        <v>3649.59</v>
+        <v>5324.76</v>
       </c>
       <c r="I118" s="5" t="n">
-        <v>3044.62</v>
-      </c>
-      <c r="J118" s="5" t="n">
-        <v>2819.43</v>
-      </c>
+        <v>5462.25</v>
+      </c>
+      <c r="J118" s="5" t="n"/>
       <c r="K118" s="5" t="n"/>
       <c r="L118" s="5" t="n"/>
       <c r="M118" s="5" t="n"/>
       <c r="N118" s="5" t="n">
-        <v>28541.07</v>
+        <v>32773.32</v>
       </c>
       <c r="O118" s="3" t="inlineStr">
         <is>
@@ -4913,36 +4886,38 @@
     <row r="119">
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>Ancy &amp; Shaya  (churned 2026-05)</t>
+          <t>Rimath  (churned 2026-06)</t>
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>3041.76</v>
+        <v>3743.36</v>
       </c>
       <c r="D119" s="5" t="n">
-        <v>2097.12</v>
+        <v>2998.75</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>2292.39</v>
+        <v>3561.57</v>
       </c>
       <c r="F119" s="5" t="n">
-        <v>2880.71</v>
+        <v>4753.24</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>2981.2</v>
+        <v>3970.51</v>
       </c>
       <c r="H119" s="5" t="n">
-        <v>2360.37</v>
+        <v>3649.59</v>
       </c>
       <c r="I119" s="5" t="n">
-        <v>1670.7</v>
-      </c>
-      <c r="J119" s="5" t="n"/>
+        <v>3044.62</v>
+      </c>
+      <c r="J119" s="5" t="n">
+        <v>2819.43</v>
+      </c>
       <c r="K119" s="5" t="n"/>
       <c r="L119" s="5" t="n"/>
       <c r="M119" s="5" t="n"/>
       <c r="N119" s="5" t="n">
-        <v>17324.25</v>
+        <v>28541.07</v>
       </c>
       <c r="O119" s="3" t="inlineStr">
         <is>
@@ -4953,30 +4928,36 @@
     <row r="120">
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>Gamesir  (churned 2026-02)</t>
+          <t>Ancy &amp; Shaya  (churned 2026-05)</t>
         </is>
       </c>
       <c r="C120" s="5" t="n">
-        <v>3161.37</v>
+        <v>3041.76</v>
       </c>
       <c r="D120" s="5" t="n">
-        <v>2732.77</v>
+        <v>2097.12</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>5143.07</v>
+        <v>2292.39</v>
       </c>
       <c r="F120" s="5" t="n">
-        <v>512.96</v>
-      </c>
-      <c r="G120" s="5" t="n"/>
-      <c r="H120" s="5" t="n"/>
-      <c r="I120" s="5" t="n"/>
+        <v>2880.71</v>
+      </c>
+      <c r="G120" s="5" t="n">
+        <v>2981.2</v>
+      </c>
+      <c r="H120" s="5" t="n">
+        <v>2360.37</v>
+      </c>
+      <c r="I120" s="5" t="n">
+        <v>1670.7</v>
+      </c>
       <c r="J120" s="5" t="n"/>
       <c r="K120" s="5" t="n"/>
       <c r="L120" s="5" t="n"/>
       <c r="M120" s="5" t="n"/>
       <c r="N120" s="5" t="n">
-        <v>11550.17</v>
+        <v>17324.25</v>
       </c>
       <c r="O120" s="3" t="inlineStr">
         <is>
@@ -4987,20 +4968,20 @@
     <row r="121">
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>Safwat Aljouf  (churned 2026-02)</t>
+          <t>Gamesir  (churned 2026-02)</t>
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>3585.43</v>
+        <v>3161.37</v>
       </c>
       <c r="D121" s="5" t="n">
-        <v>2564.26</v>
+        <v>2732.77</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>2607.58</v>
+        <v>5143.07</v>
       </c>
       <c r="F121" s="5" t="n">
-        <v>837.29</v>
+        <v>512.96</v>
       </c>
       <c r="G121" s="5" t="n"/>
       <c r="H121" s="5" t="n"/>
@@ -5010,7 +4991,7 @@
       <c r="L121" s="5" t="n"/>
       <c r="M121" s="5" t="n"/>
       <c r="N121" s="5" t="n">
-        <v>9594.559999999999</v>
+        <v>11550.17</v>
       </c>
       <c r="O121" s="3" t="inlineStr">
         <is>
@@ -5021,30 +5002,30 @@
     <row r="122">
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>Reetal  (churned 2026-06)</t>
-        </is>
-      </c>
-      <c r="C122" s="5" t="n"/>
-      <c r="D122" s="5" t="n"/>
-      <c r="E122" s="5" t="n"/>
-      <c r="F122" s="5" t="n"/>
-      <c r="G122" s="5" t="n">
-        <v>4492.3</v>
-      </c>
-      <c r="H122" s="5" t="n">
-        <v>1033.1</v>
-      </c>
-      <c r="I122" s="5" t="n">
-        <v>1799.32</v>
-      </c>
-      <c r="J122" s="5" t="n">
-        <v>684.49</v>
-      </c>
+          <t>Safwat Aljouf  (churned 2026-02)</t>
+        </is>
+      </c>
+      <c r="C122" s="5" t="n">
+        <v>3585.43</v>
+      </c>
+      <c r="D122" s="5" t="n">
+        <v>2564.26</v>
+      </c>
+      <c r="E122" s="5" t="n">
+        <v>2607.58</v>
+      </c>
+      <c r="F122" s="5" t="n">
+        <v>837.29</v>
+      </c>
+      <c r="G122" s="5" t="n"/>
+      <c r="H122" s="5" t="n"/>
+      <c r="I122" s="5" t="n"/>
+      <c r="J122" s="5" t="n"/>
       <c r="K122" s="5" t="n"/>
       <c r="L122" s="5" t="n"/>
       <c r="M122" s="5" t="n"/>
       <c r="N122" s="5" t="n">
-        <v>8009.21</v>
+        <v>9594.559999999999</v>
       </c>
       <c r="O122" s="3" t="inlineStr">
         <is>
@@ -5055,179 +5036,239 @@
     <row r="123">
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>House Mart  (churned 2026-04)</t>
-        </is>
-      </c>
-      <c r="C123" s="5" t="n">
-        <v>6750</v>
-      </c>
+          <t>Reetal  (churned 2026-06)</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="n"/>
       <c r="D123" s="5" t="n"/>
       <c r="E123" s="5" t="n"/>
       <c r="F123" s="5" t="n"/>
-      <c r="G123" s="5" t="n"/>
+      <c r="G123" s="5" t="n">
+        <v>4492.3</v>
+      </c>
       <c r="H123" s="5" t="n">
-        <v>8800.5</v>
-      </c>
-      <c r="I123" s="5" t="n"/>
-      <c r="J123" s="5" t="n"/>
+        <v>1033.1</v>
+      </c>
+      <c r="I123" s="5" t="n">
+        <v>1799.32</v>
+      </c>
+      <c r="J123" s="5" t="n">
+        <v>684.49</v>
+      </c>
       <c r="K123" s="5" t="n"/>
       <c r="L123" s="5" t="n"/>
       <c r="M123" s="5" t="n"/>
       <c r="N123" s="5" t="n">
+        <v>8009.21</v>
+      </c>
+      <c r="O123" s="3" t="inlineStr">
+        <is>
+          <t>Wafeq invoice export</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>House Mart  (churned 2026-04)</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="n">
+        <v>6750</v>
+      </c>
+      <c r="D124" s="5" t="n"/>
+      <c r="E124" s="5" t="n"/>
+      <c r="F124" s="5" t="n"/>
+      <c r="G124" s="5" t="n"/>
+      <c r="H124" s="5" t="n">
+        <v>8800.5</v>
+      </c>
+      <c r="I124" s="5" t="n"/>
+      <c r="J124" s="5" t="n"/>
+      <c r="K124" s="5" t="n"/>
+      <c r="L124" s="5" t="n"/>
+      <c r="M124" s="5" t="n"/>
+      <c r="N124" s="5" t="n">
         <v>15550.5</v>
       </c>
-      <c r="O123" s="3" t="inlineStr">
+      <c r="O124" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="B124" s="6" t="inlineStr">
+    <row r="125">
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>Al Safa  (new — first invoice Oct 2026)</t>
+        </is>
+      </c>
+      <c r="C125" s="5" t="n"/>
+      <c r="D125" s="5" t="n"/>
+      <c r="E125" s="5" t="n"/>
+      <c r="F125" s="5" t="n"/>
+      <c r="G125" s="5" t="n"/>
+      <c r="H125" s="5" t="n"/>
+      <c r="I125" s="5" t="n"/>
+      <c r="J125" s="5" t="n"/>
+      <c r="K125" s="5" t="n"/>
+      <c r="L125" s="5" t="n"/>
+      <c r="M125" s="5" t="n"/>
+      <c r="N125" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" s="3" t="inlineStr">
+        <is>
+          <t>Wafeq invoice export</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" s="6" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C124" s="7" t="n">
+      <c r="C126" s="7" t="n">
         <v>31390.44</v>
       </c>
-      <c r="D124" s="7" t="n">
+      <c r="D126" s="7" t="n">
         <v>21947.73</v>
       </c>
-      <c r="E124" s="7" t="n">
+      <c r="E126" s="7" t="n">
         <v>26212.8</v>
       </c>
-      <c r="F124" s="7" t="n">
+      <c r="F126" s="7" t="n">
         <v>19517.67</v>
       </c>
-      <c r="G124" s="7" t="n">
+      <c r="G126" s="7" t="n">
         <v>27125.53</v>
       </c>
-      <c r="H124" s="7" t="n">
+      <c r="H126" s="7" t="n">
         <v>27486.22</v>
       </c>
-      <c r="I124" s="7" t="n">
+      <c r="I126" s="7" t="n">
         <v>21956.43</v>
       </c>
-      <c r="J124" s="7" t="n">
+      <c r="J126" s="7" t="n">
         <v>16243.45</v>
       </c>
-      <c r="K124" s="7" t="n">
+      <c r="K126" s="7" t="n">
         <v>7298.95</v>
       </c>
-      <c r="L124" s="7" t="n">
+      <c r="L126" s="7" t="n">
         <v>12694.6</v>
       </c>
-      <c r="M124" s="7" t="n">
+      <c r="M126" s="7" t="n">
         <v>10148.67</v>
       </c>
-      <c r="N124" s="7" t="n">
+      <c r="N126" s="7" t="n">
         <v>222022.49</v>
       </c>
-      <c r="O124" s="3" t="inlineStr">
+      <c r="O126" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="B126" s="1" t="inlineStr">
+    <row r="128">
+      <c r="B128" s="1" t="inlineStr">
         <is>
           <t>PLATFORM MAPPING CHECK</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="B127" s="3" t="inlineStr">
-        <is>
-          <t>Read 2026-10-11 · checked against the 2026-09 issued invoices · 5 of 11 clients read from the platform · 2026-09 is drafted, not released</t>
-        </is>
-      </c>
-      <c r="O127" s="3" t="inlineStr">
-        <is>
-          <t>Nasam platform billing — NASAM-ORG-* invoice line items (September, as issued), plus the تعديل المنظمة dialog for switched-off channels</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="B128" s="3" t="inlineStr">
-        <is>
-          <t>Note: Alfaris Group · Salla</t>
-        </is>
-      </c>
-      <c r="O128" s="3" t="inlineStr">
-        <is>
-          <t>commission off by agreement — 156,898 of sales in 2026-09 earns nothing and is shown for visibility only</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="B129" s="3" t="inlineStr">
         <is>
+          <t>Read 2026-10-11 · checked against the 2026-09 issued invoices · 5 of 11 clients read from the platform · 2026-09 is drafted, not released</t>
+        </is>
+      </c>
+      <c r="O129" s="3" t="inlineStr">
+        <is>
+          <t>Nasam platform billing — NASAM-ORG-* invoice line items (September, as issued), plus the تعديل المنظمة dialog for switched-off channels</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>Note: Alfaris Group · Salla</t>
+        </is>
+      </c>
+      <c r="O130" s="3" t="inlineStr">
+        <is>
+          <t>commission off by agreement — 156,898 of sales in 2026-09 earns nothing and is shown for visibility only</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" s="3" t="inlineStr">
+        <is>
           <t>Note: Dar Sonbol · Salla</t>
         </is>
       </c>
-      <c r="O129" s="3" t="inlineStr">
-        <is>
-          <t>commission off by agreement — 681,572 of sales in 2026-09 earns nothing and is shown for visibility only</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>Decide: Dar Sonbol</t>
-        </is>
-      </c>
-      <c r="O130" s="3" t="inlineStr">
-        <is>
-          <t>organization record holds 8,000/mo and no RELEASED invoice has ever charged it — the one that does is still in draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>Decide: Inivita · Salla</t>
-        </is>
-      </c>
       <c r="O131" s="3" t="inlineStr">
         <is>
-          <t>connected 10 Sep 2026 and sold 215,870 in September. The September invoice has now been ISSUED itemising Amazon, Noon and Trendyol with no Salla line, so the month is billed and closed without it — is it 7% like Invita's other channels, or no-commission like the other Salla stores?</t>
+          <t>commission off by agreement — 677,237 of sales in 2026-09 earns nothing and is shown for visibility only</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="B132" s="1" t="inlineStr">
         <is>
+          <t>Decide: Dar Sonbol</t>
+        </is>
+      </c>
+      <c r="O132" s="3" t="inlineStr">
+        <is>
+          <t>organization record holds 8,000/mo and no RELEASED invoice has ever charged it — the one that does is still in draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" s="1" t="inlineStr">
+        <is>
+          <t>Decide: Inivita · Salla</t>
+        </is>
+      </c>
+      <c r="O133" s="3" t="inlineStr">
+        <is>
+          <t>connected 10 Sep 2026 and sold 215,870 in September. The September invoice has now been ISSUED itemising Amazon, Noon and Trendyol with no Salla line, so the month is billed and closed without it — is it 7% like Invita's other channels, or no-commission like the other Salla stores?</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" s="1" t="inlineStr">
+        <is>
           <t>Decide: Wadi Halfa · Ninja Retail</t>
         </is>
       </c>
-      <c r="O132" s="3" t="inlineStr">
+      <c r="O134" s="3" t="inlineStr">
         <is>
           <t>billed by hand at 4%; the platform has never produced a Ninja Retail line, including on the released September invoice, against 13,232 received — 242.04 booked in the window by hand</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="B133" s="3" t="inlineStr">
+    <row r="135">
+      <c r="B135" s="3" t="inlineStr">
         <is>
           <t>Drafted: Dar Sonbol</t>
         </is>
       </c>
-      <c r="O133" s="3" t="inlineStr">
+      <c r="O135" s="3" t="inlineStr">
         <is>
           <t>drafted 8,000.00 for 2026-09 (fee 8,000) — NASAM-ORG-86-09-2026 — the only September invoice NOT released. It is the first document ever raised for this client beyond the June setup fee and the first to charge the 8,000; until it is released Dar Sonbol has still never been billed a fee, against 681,572 of September Salla sales</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="B134" s="3" t="inlineStr">
+    <row r="136">
+      <c r="B136" s="3" t="inlineStr">
         <is>
           <t>Note: Ancy &amp; Shaya, Gamesir, Reetal, Rimath, Safwat Aljouf, Two United</t>
         </is>
       </c>
-      <c r="O134" s="3" t="inlineStr">
+      <c r="O136" s="3" t="inlineStr">
         <is>
           <t>no platform invoice to read — still on rate-card terms</t>
         </is>
@@ -5639,10 +5680,10 @@
         <v>618.75</v>
       </c>
       <c r="Q6" s="14" t="n">
-        <v>373.03</v>
+        <v>376.8</v>
       </c>
       <c r="R6" s="14" t="n">
-        <v>1625.4</v>
+        <v>1629.17</v>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
@@ -6064,10 +6105,10 @@
         <v>1072.9</v>
       </c>
       <c r="Q13" s="14" t="n">
-        <v>959.89</v>
+        <v>969.59</v>
       </c>
       <c r="R13" s="14" t="n">
-        <v>2869.6</v>
+        <v>2879.3</v>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
@@ -6125,10 +6166,10 @@
         <v>60173.92</v>
       </c>
       <c r="Q14" s="12" t="n">
-        <v>199091.93</v>
+        <v>198441.57</v>
       </c>
       <c r="R14" s="12" t="n">
-        <v>646833.5</v>
+        <v>646183.14</v>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
@@ -6546,10 +6587,10 @@
         <v>20575.62</v>
       </c>
       <c r="Q21" s="12" t="n">
-        <v>39893.79</v>
+        <v>39243.43</v>
       </c>
       <c r="R21" s="12" t="n">
-        <v>79872.42</v>
+        <v>79222.06</v>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
@@ -6617,10 +6658,10 @@
         <v>1267.31</v>
       </c>
       <c r="Q22" s="14" t="n">
-        <v>2422.94</v>
+        <v>2407.52</v>
       </c>
       <c r="R22" s="14" t="n">
-        <v>5109.94</v>
+        <v>5094.53</v>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
@@ -6955,10 +6996,10 @@
         <v>628.03</v>
       </c>
       <c r="Q28" s="14" t="n">
-        <v>192.58</v>
+        <v>194.53</v>
       </c>
       <c r="R28" s="14" t="n">
-        <v>1401.55</v>
+        <v>1403.5</v>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
@@ -9174,13 +9215,13 @@
       <c r="N70" s="12" t="n"/>
       <c r="O70" s="12" t="n"/>
       <c r="P70" s="12" t="n">
-        <v>556932.3</v>
+        <v>557236.5</v>
       </c>
       <c r="Q70" s="12" t="n">
-        <v>681572.34</v>
+        <v>677237.1800000001</v>
       </c>
       <c r="R70" s="12" t="n">
-        <v>1238504.64</v>
+        <v>1234473.68</v>
       </c>
       <c r="S70" s="3" t="inlineStr">
         <is>
@@ -16654,7 +16695,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N63"/>
+  <dimension ref="A1:N64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -18013,18 +18054,16 @@
           <t>Ancy &amp; Shaya</t>
         </is>
       </c>
-      <c r="C51" s="15" t="n"/>
+      <c r="C51" s="15" t="n">
+        <v>0.27</v>
+      </c>
       <c r="D51" s="15" t="n">
         <v>7012.27</v>
       </c>
       <c r="E51" s="15" t="n">
-        <v>-7012.27</v>
-      </c>
-      <c r="F51" s="3" t="inlineStr">
-        <is>
-          <t>Pass-through contact — excluded from revenue, still an open balance</t>
-        </is>
-      </c>
+        <v>-7012</v>
+      </c>
+      <c r="F51" s="3" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="B52" s="3" t="inlineStr">
@@ -18120,56 +18159,71 @@
       </c>
     </row>
     <row r="57">
-      <c r="B57" s="1" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Al Safa</t>
+        </is>
+      </c>
+      <c r="C57" s="15" t="n">
+        <v>5499</v>
+      </c>
+      <c r="D57" s="15" t="n"/>
+      <c r="E57" s="15" t="n">
+        <v>5499</v>
+      </c>
+      <c r="F57" s="3" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="B58" s="1" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C57" s="18" t="n">
-        <v>66525.03</v>
-      </c>
-      <c r="D57" s="18" t="n">
+      <c r="C58" s="18" t="n">
+        <v>72024.3</v>
+      </c>
+      <c r="D58" s="18" t="n">
         <v>49383.19</v>
       </c>
-      <c r="E57" s="18" t="n">
-        <v>17141.84</v>
-      </c>
-      <c r="F57" s="1" t="inlineStr">
+      <c r="E58" s="18" t="n">
+        <v>22641.11</v>
+      </c>
+      <c r="F58" s="1" t="inlineStr">
         <is>
           <t>Statement rows tie to debit less credit (49,383.19); its printed footer says 45,165.51 — with the accountant</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="B59" s="1" t="inlineStr">
+    <row r="60">
+      <c r="B60" s="1" t="inlineStr">
         <is>
           <t>Read this sheet with care</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="28" customHeight="1">
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>Cost is on a cash-recorded basis: a bill lands in the month it was entered, so months are lumpy (accounting fees, insurance and government fees arrive in blocks).</t>
         </is>
       </c>
     </row>
     <row r="61" ht="28" customHeight="1">
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Salaries come from the journal, bills from the purchase ledger. Nothing here is accrued or apportioned.</t>
+          <t>Cost is on a cash-recorded basis: a bill lands in the month it was entered, so months are lumpy (accounting fees, insurance and government fees arrive in blocks).</t>
         </is>
       </c>
     </row>
     <row r="62" ht="28" customHeight="1">
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>The client-side block is excluded from operating cost on purpose. Until each line is confirmed as rebilled or absorbed, the true cost sits between the two totals.</t>
+          <t>Salaries come from the journal, bills from the purchase ledger. Nothing here is accrued or apportioned.</t>
         </is>
       </c>
     </row>
     <row r="63" ht="28" customHeight="1">
       <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>The client-side block is excluded from operating cost on purpose. Until each line is confirmed as rebilled or absorbed, the true cost sits between the two totals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="28" customHeight="1">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>Partner contributions are how the gap has been funded to date. They are not revenue and never enter the revenue sheets.</t>
         </is>

--- a/revenue-view/output/Nasam_Revenue_View.xlsx
+++ b/revenue-view/output/Nasam_Revenue_View.xlsx
@@ -497,7 +497,7 @@
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Nasam Revenue View — weekly run · 18 Oct 2026</t>
+          <t>Nasam Revenue View — weekly run · 25 Oct 2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr"/>
@@ -510,7 +510,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nasam has signed a client. مستودع الصفا للأدوية المحدودة (Al Safa) was invoiced 5,499 on 13 Oct — a setup fee for onboarding to Amazon, Trendyol and Noon with inventory integration. It is the first new client to be billed since the churn began in February, and the first setup fee since Dar Sonbol in June. The invoice is dated October, so it sits outside this window and is shown as a memo under the revenue streams rather than in any total; it enters billed when October closes. Nothing else moved on billing: the window stays at 222,022.49 and Dar Sonbol's 8,000 is still the one September invoice in draft, now a fortnight old. One small reversal — 0.27 of the Ancy &amp; Shaya balance settled last week has reopened, leaving that account all but clear. September sales continue to settle downward as late cancellations land: Sonbol 677,237 and SONDOS Trendyol 39,243, both trimmed again this week.</t>
+          <t>Dar Sonbol's 8,000 September invoice has been DELETED from Wafeq rather than released, so that client has still never been billed a fee of any kind — against 674,790 of September Salla sales. Nothing is in draft now. Al Safa, the new client, is moving quickly: a second invoice on 22 Oct for 2,990, a Salla subscription, taking its October billing to 8,489; and its store Al-safa Care was connected to the platform on 20 Oct, arriving with a year of backfilled Salla history worth roughly 430,000. That backfill predates the integration, so every month of it is excluded on the same rule as Sonbol and Invita — only the 2,699 earned since 20 Oct is Nasam's, and that falls in October. The window itself is unchanged at 222,022.49 billed. Two older figures were restated again this week, Sense Trendyol in June and SONDOS Salla in September.</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Wafeq API snapshot 18 Oct (170 invoices — one new client, INV-000193) · platform commission mapping read 11 Oct from the September invoices as issued (5 clients; no October invoices raised yet) · platform sales and purchase orders pulled 18 Oct · Wafeq accounting exports 8 Sep: purchase bills, journal entries, customer-balances statement · churned-brand snapshots 15 Aug (frozen) · Salla Partners export 30 Aug (49 days old — the four trials live then have all since expired) · rate card 17 Aug. The closed-PO export is retired: purchase orders now carry their values in the platform read layer.</t>
+          <t>Wafeq API snapshot 25 Oct (170 invoices — INV00194 added, NASAM-ORG-86-09-2026 deleted) · platform commission mapping read 11 Oct from the September invoices as issued (5 clients; no October invoices raised yet) · platform sales and purchase orders pulled 25 Oct · Wafeq accounting exports 8 Sep: purchase bills, journal entries, customer-balances statement · churned-brand snapshots 15 Aug (frozen) · Salla Partners export 30 Aug (56 days old — the four trials live then have all since expired) · rate card 17 Aug. The closed-PO export is retired: purchase orders now carry their values in the platform read layer.</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
         <v>107398.15</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>47085.98</v>
+        <v>46956.83</v>
       </c>
       <c r="K3" s="5" t="n">
         <v>32371.27</v>
@@ -713,7 +713,7 @@
         <v>306339.35</v>
       </c>
       <c r="N3" s="5" t="n">
-        <v>1266634.57</v>
+        <v>1266505.42</v>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
@@ -823,13 +823,13 @@
         <v>220575.12</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>600568.0600000001</v>
+        <v>600263.86</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>834135.42</v>
+        <v>831493.66</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>1943999.19</v>
+        <v>1941053.23</v>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
@@ -865,19 +865,19 @@
         <v>286489.12</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>136622.4</v>
+        <v>136493.25</v>
       </c>
       <c r="K7" s="7" t="n">
         <v>259520.94</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>713872.52</v>
+        <v>713568.3199999999</v>
       </c>
       <c r="M7" s="7" t="n">
-        <v>1167059.05</v>
+        <v>1164417.29</v>
       </c>
       <c r="N7" s="7" t="n">
-        <v>3312556.09</v>
+        <v>3309480.98</v>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>79072.67999999999</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>111585.16</v>
+        <v>111456.01</v>
       </c>
       <c r="K9" s="8" t="n">
         <v>233096.91</v>
@@ -929,10 +929,10 @@
         <v>112057.45</v>
       </c>
       <c r="M9" s="8" t="n">
-        <v>232170.71</v>
+        <v>231976.16</v>
       </c>
       <c r="N9" s="8" t="n">
-        <v>850996.89</v>
+        <v>850673.1899999999</v>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
@@ -1289,10 +1289,10 @@
         <v>60173.92</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>198441.57</v>
+        <v>198247.02</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>646183.14</v>
+        <v>645988.59</v>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
@@ -1441,10 +1441,10 @@
         <v>36095.94</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>154308.44</v>
+        <v>154113.89</v>
       </c>
       <c r="N22" s="5" t="n">
-        <v>532088.63</v>
+        <v>531894.08</v>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>5097.23</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>8631.34</v>
+        <v>8502.190000000001</v>
       </c>
       <c r="K24" s="5" t="n">
         <v>5624.82</v>
@@ -1528,7 +1528,7 @@
         <v>3805.64</v>
       </c>
       <c r="N24" s="5" t="n">
-        <v>36926.22</v>
+        <v>36797.07</v>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>1345.56</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>6588.79</v>
+        <v>6459.64</v>
       </c>
       <c r="K27" s="5" t="n">
         <v>745.47</v>
@@ -1632,7 +1632,7 @@
         <v>3170.88</v>
       </c>
       <c r="N27" s="5" t="n">
-        <v>22047.13</v>
+        <v>21917.98</v>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
@@ -2270,13 +2270,13 @@
       <c r="J43" s="5" t="n"/>
       <c r="K43" s="5" t="n"/>
       <c r="L43" s="5" t="n">
-        <v>557236.5</v>
+        <v>556932.3</v>
       </c>
       <c r="M43" s="5" t="n">
-        <v>677237.1800000001</v>
+        <v>674789.97</v>
       </c>
       <c r="N43" s="5" t="n">
-        <v>1234473.68</v>
+        <v>1231722.27</v>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
@@ -4371,11 +4371,9 @@
       <c r="J102" s="5" t="n"/>
       <c r="K102" s="5" t="n"/>
       <c r="L102" s="5" t="n"/>
-      <c r="M102" s="5" t="n">
-        <v>8000</v>
-      </c>
+      <c r="M102" s="5" t="n"/>
       <c r="N102" s="5" t="n">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="O102" s="3" t="inlineStr">
         <is>
@@ -4390,7 +4388,7 @@
         </is>
       </c>
       <c r="N103" s="5" t="n">
-        <v>5499</v>
+        <v>8489</v>
       </c>
       <c r="O103" s="3" t="inlineStr">
         <is>
@@ -5181,7 +5179,7 @@
     <row r="129">
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>Read 2026-10-11 · checked against the 2026-09 issued invoices · 5 of 11 clients read from the platform · 2026-09 is drafted, not released</t>
+          <t>Read 2026-10-25 · checked against the 2026-09 issued invoices · 5 of 11 clients read from the platform · 2026-09 is drafted, not released</t>
         </is>
       </c>
       <c r="O129" s="3" t="inlineStr">
@@ -5198,7 +5196,7 @@
       </c>
       <c r="O130" s="3" t="inlineStr">
         <is>
-          <t>commission off by agreement — 156,898 of sales in 2026-09 earns nothing and is shown for visibility only</t>
+          <t>commission off by agreement — 156,704 of sales in 2026-09 earns nothing and is shown for visibility only</t>
         </is>
       </c>
     </row>
@@ -5210,7 +5208,7 @@
       </c>
       <c r="O131" s="3" t="inlineStr">
         <is>
-          <t>commission off by agreement — 677,237 of sales in 2026-09 earns nothing and is shown for visibility only</t>
+          <t>commission off by agreement — 674,790 of sales in 2026-09 earns nothing and is shown for visibility only</t>
         </is>
       </c>
     </row>
@@ -5229,36 +5227,36 @@
     <row r="133">
       <c r="B133" s="1" t="inlineStr">
         <is>
-          <t>Decide: Inivita · Salla</t>
+          <t>Decide: Al Safa · Salla</t>
         </is>
       </c>
       <c r="O133" s="3" t="inlineStr">
         <is>
-          <t>connected 10 Sep 2026 and sold 215,870 in September. The September invoice has now been ISSUED itemising Amazon, Noon and Trendyol with no Salla line, so the month is billed and closed without it — is it 7% like Invita's other channels, or no-commission like the other Salla stores?</t>
+          <t>signed Oct 2026 — two invoices so far (5,499 setup, 2,990 Salla subscription) and no commercial terms recorded: no rate per channel and no monthly fee, so nothing to check its first commission month against</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="B134" s="1" t="inlineStr">
         <is>
+          <t>Decide: Inivita · Salla</t>
+        </is>
+      </c>
+      <c r="O134" s="3" t="inlineStr">
+        <is>
+          <t>connected 10 Sep 2026 and sold 215,870 in September. The September invoice has now been ISSUED itemising Amazon, Noon and Trendyol with no Salla line, so the month is billed and closed without it — is it 7% like Invita's other channels, or no-commission like the other Salla stores?</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="B135" s="1" t="inlineStr">
+        <is>
           <t>Decide: Wadi Halfa · Ninja Retail</t>
         </is>
       </c>
-      <c r="O134" s="3" t="inlineStr">
+      <c r="O135" s="3" t="inlineStr">
         <is>
           <t>billed by hand at 4%; the platform has never produced a Ninja Retail line, including on the released September invoice, against 13,232 received — 242.04 booked in the window by hand</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="B135" s="3" t="inlineStr">
-        <is>
-          <t>Drafted: Dar Sonbol</t>
-        </is>
-      </c>
-      <c r="O135" s="3" t="inlineStr">
-        <is>
-          <t>drafted 8,000.00 for 2026-09 (fee 8,000) — NASAM-ORG-86-09-2026 — the only September invoice NOT released. It is the first document ever raised for this client beyond the June setup fee and the first to charge the 8,000; until it is released Dar Sonbol has still never been billed a fee, against 681,572 of September Salla sales</t>
         </is>
       </c>
     </row>
@@ -5671,7 +5669,7 @@
         <v>167.82</v>
       </c>
       <c r="N6" s="14" t="n">
-        <v>235.76</v>
+        <v>237.71</v>
       </c>
       <c r="O6" s="14" t="n">
         <v>230.03</v>
@@ -5683,7 +5681,7 @@
         <v>376.8</v>
       </c>
       <c r="R6" s="14" t="n">
-        <v>1629.17</v>
+        <v>1631.11</v>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
@@ -6096,7 +6094,7 @@
         <v>483.37</v>
       </c>
       <c r="N13" s="14" t="n">
-        <v>231.11</v>
+        <v>233.02</v>
       </c>
       <c r="O13" s="14" t="n">
         <v>73.31</v>
@@ -6108,7 +6106,7 @@
         <v>969.59</v>
       </c>
       <c r="R13" s="14" t="n">
-        <v>2879.3</v>
+        <v>2881.21</v>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
@@ -6166,10 +6164,10 @@
         <v>60173.92</v>
       </c>
       <c r="Q14" s="12" t="n">
-        <v>198441.57</v>
+        <v>198247.02</v>
       </c>
       <c r="R14" s="12" t="n">
-        <v>646183.14</v>
+        <v>645988.59</v>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
@@ -6520,10 +6518,10 @@
         <v>36095.94</v>
       </c>
       <c r="Q20" s="12" t="n">
-        <v>154308.44</v>
+        <v>154113.89</v>
       </c>
       <c r="R20" s="12" t="n">
-        <v>532088.63</v>
+        <v>531894.08</v>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
@@ -6649,7 +6647,7 @@
         <v>191.84</v>
       </c>
       <c r="N22" s="14" t="n">
-        <v>142.4</v>
+        <v>143.58</v>
       </c>
       <c r="O22" s="14" t="n">
         <v>78.84999999999999</v>
@@ -6661,7 +6659,7 @@
         <v>2407.52</v>
       </c>
       <c r="R22" s="14" t="n">
-        <v>5094.53</v>
+        <v>5095.7</v>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
@@ -6700,7 +6698,7 @@
         <v>5097.23</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>8631.34</v>
+        <v>8502.190000000001</v>
       </c>
       <c r="O23" s="12" t="n">
         <v>5624.82</v>
@@ -6712,7 +6710,7 @@
         <v>3805.64</v>
       </c>
       <c r="R23" s="12" t="n">
-        <v>36926.22</v>
+        <v>36797.07</v>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
@@ -6926,7 +6924,7 @@
         <v>1345.56</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>6588.79</v>
+        <v>6459.64</v>
       </c>
       <c r="O27" s="12" t="n">
         <v>745.47</v>
@@ -6938,7 +6936,7 @@
         <v>3170.88</v>
       </c>
       <c r="R27" s="12" t="n">
-        <v>22047.13</v>
+        <v>21917.98</v>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
@@ -6987,7 +6985,7 @@
         <v>98.2</v>
       </c>
       <c r="N28" s="14" t="n">
-        <v>436.46</v>
+        <v>431.44</v>
       </c>
       <c r="O28" s="14" t="n">
         <v>46.28</v>
@@ -6999,7 +6997,7 @@
         <v>194.53</v>
       </c>
       <c r="R28" s="14" t="n">
-        <v>1403.5</v>
+        <v>1398.47</v>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
@@ -9215,13 +9213,13 @@
       <c r="N70" s="12" t="n"/>
       <c r="O70" s="12" t="n"/>
       <c r="P70" s="12" t="n">
-        <v>557236.5</v>
+        <v>556932.3</v>
       </c>
       <c r="Q70" s="12" t="n">
-        <v>677237.1800000001</v>
+        <v>674789.97</v>
       </c>
       <c r="R70" s="12" t="n">
-        <v>1234473.68</v>
+        <v>1231722.27</v>
       </c>
       <c r="S70" s="3" t="inlineStr">
         <is>
@@ -18165,11 +18163,11 @@
         </is>
       </c>
       <c r="C57" s="15" t="n">
-        <v>5499</v>
+        <v>8489</v>
       </c>
       <c r="D57" s="15" t="n"/>
       <c r="E57" s="15" t="n">
-        <v>5499</v>
+        <v>8489</v>
       </c>
       <c r="F57" s="3" t="inlineStr"/>
     </row>
@@ -18180,13 +18178,13 @@
         </is>
       </c>
       <c r="C58" s="18" t="n">
-        <v>72024.3</v>
+        <v>75014.3</v>
       </c>
       <c r="D58" s="18" t="n">
         <v>49383.19</v>
       </c>
       <c r="E58" s="18" t="n">
-        <v>22641.11</v>
+        <v>25631.11</v>
       </c>
       <c r="F58" s="1" t="inlineStr">
         <is>
